--- a/output/pdf_financials_xlsx/TOT.xlsx
+++ b/output/pdf_financials_xlsx/TOT.xlsx
@@ -6406,31 +6406,31 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>5.148</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>5.875</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>7.588</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>8.422000000000001</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>10.507</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>6.292</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>11.516</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>2.315</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>24.431</v>
       </c>
     </row>
     <row r="113">
@@ -17868,7 +17868,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -22954,7 +22958,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TOT.xlsx
+++ b/output/pdf_financials_xlsx/TOT.xlsx
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.058</v>
+        <v>-1.95</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.166</v>
+        <v>3.506</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-3.243</v>
+        <v>2.07</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3.629</v>
+        <v>0.161</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.862</v>
@@ -2203,16 +2203,16 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-25.40696218382169</v>
+        <v>-12.20886551465064</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-23.104</v>
+        <v>-37.39733333333334</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12.77375137860406</v>
+        <v>8.153458326768552</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>57.5940326932233</v>
+        <v>2.555149976194255</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-22.17648572163623</v>
@@ -6465,10 +6465,10 @@
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0</v>
+        <v>-10.855</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0</v>
+        <v>-26.83</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>0</v>
@@ -6955,31 +6955,31 @@
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-4.191</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-5.346</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-12.638</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-13.587</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-21.474</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-24.158</v>
       </c>
     </row>
     <row r="122">
@@ -9468,7 +9468,11 @@
           <t>Lease liabilities 15</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -11142,7 +11146,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12590,7 +12598,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -16972,7 +16984,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -18442,7 +18458,11 @@
           <t>Repurchase of common shares 17</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -19464,7 +19484,11 @@
           <t>Deferred income tax expense 15</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -20362,7 +20386,11 @@
           <t>Repurchase of common shares 16</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -21030,7 +21058,11 @@
           <t>Deferred income tax expense 14</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -21798,7 +21830,11 @@
           <t>Repurchase of common shares 15</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -22216,7 +22252,11 @@
           <t>Deferred income tax expense (recovery) 15</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -23624,7 +23664,11 @@
           <t>Deferred income tax expense (recovery) 16</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -23878,7 +23922,11 @@
           <t>Acquisition of business 5</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -24646,7 +24694,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -35532,7 +35584,11 @@
           <t>Current income tax recovery 15</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -37886,7 +37942,11 @@
           <t>Current income tax recovery 16</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -40594,7 +40654,11 @@
           <t>Current income tax (recovery) expense 16</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -40674,7 +40738,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -40754,7 +40822,11 @@
           <t>Total income tax recovery 16</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
